--- a/services/sim/lms/bins_data.xlsx
+++ b/services/sim/lms/bins_data.xlsx
@@ -529,14 +529,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>420134</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>黄鹤楼（硬1916）</t>
         </is>
       </c>
     </row>
@@ -28269,11 +28272,16 @@
         </is>
       </c>
       <c r="H629" t="n">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>450123</t>
+        </is>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>钻石（硬迎宾）</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -28308,19 +28316,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H630" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H630" t="n">
+        <v>18</v>
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>046909</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>云烟(紫)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -28355,19 +28361,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H631" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H631" t="n">
+        <v>30</v>
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>062367</t>
+          <t>130688</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>南京(十二钗薄荷)</t>
+          <t>钻石（细支尚风）</t>
         </is>
       </c>
     </row>
@@ -28403,11 +28407,16 @@
         </is>
       </c>
       <c r="H632" t="n">
-        <v>5</v>
+        <v>30</v>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>130688</t>
+        </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>钻石（细支尚风）</t>
         </is>
       </c>
     </row>
@@ -28442,19 +28451,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H633" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H633" t="n">
+        <v>30</v>
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>121743</t>
+          <t>130688</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>利群(楼外楼)</t>
+          <t>钻石（细支尚风）</t>
         </is>
       </c>
     </row>

--- a/services/sim/lms/bins_data.xlsx
+++ b/services/sim/lms/bins_data.xlsx
@@ -23460,14 +23460,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H521" t="n">
+        <v>18</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23502,19 +23505,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H522" t="n">
+        <v>18</v>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>077897</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>钻石(硬迎宾)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23549,19 +23550,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H523" t="n">
+        <v>18</v>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>160292</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>黄金叶(乐途)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23596,14 +23595,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H524" t="n">
+        <v>18</v>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23638,19 +23640,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H525" t="n">
+        <v>18</v>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>075121</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>中华(硬)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23685,19 +23685,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H526" t="n">
+        <v>18</v>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>077897</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>钻石(硬迎宾)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23732,14 +23730,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H527" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H527" t="n">
+        <v>18</v>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23774,19 +23775,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H528" t="n">
+        <v>18</v>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>250658</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>钻石(软红)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23821,19 +23820,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H529" t="n">
+        <v>18</v>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>169585</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>黄金叶(金满堂)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23868,14 +23865,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H530" t="n">
+        <v>18</v>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23910,19 +23910,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H531" t="n">
+        <v>18</v>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>169585</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>黄金叶(金满堂)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -23957,19 +23955,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H532" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H532" t="n">
+        <v>18</v>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>169585</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>黄金叶(金满堂)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24004,14 +24000,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H533" t="n">
+        <v>18</v>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24046,19 +24045,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H534" t="n">
+        <v>18</v>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>339964</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>云烟(细支云龙)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24093,19 +24090,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H535" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H535" t="n">
+        <v>18</v>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>159760</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>泰山(心悦)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24140,14 +24135,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H536" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H536" t="n">
+        <v>18</v>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24182,19 +24180,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H537" t="n">
+        <v>18</v>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>339964</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>云烟(细支云龙)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24229,19 +24225,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H538" t="n">
+        <v>18</v>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>159760</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>泰山(心悦)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24276,14 +24270,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H539" t="n">
+        <v>18</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24318,19 +24315,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H540" t="n">
+        <v>18</v>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>224086</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>金圣(滕王阁.紫光)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24365,14 +24360,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H541" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H541" t="n">
+        <v>18</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24407,14 +24405,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H542" t="n">
+        <v>18</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24449,19 +24450,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H543" t="n">
+        <v>18</v>
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>077897</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>钻石(硬迎宾)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24496,14 +24495,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H544" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H544" t="n">
+        <v>18</v>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24538,14 +24540,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H545" t="n">
+        <v>18</v>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24580,14 +24585,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H546" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H546" t="n">
+        <v>18</v>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24622,14 +24630,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H547" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H547" t="n">
+        <v>18</v>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24664,14 +24675,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H548" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H548" t="n">
+        <v>18</v>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24706,19 +24720,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H549" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H549" t="n">
+        <v>18</v>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>250658</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>钻石(软红)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24753,14 +24765,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H550" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H550" t="n">
+        <v>18</v>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24795,14 +24810,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H551" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H551" t="n">
+        <v>18</v>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24837,14 +24855,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H552" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H552" t="n">
+        <v>18</v>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24879,14 +24900,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H553" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H553" t="n">
+        <v>18</v>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24921,14 +24945,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H554" t="n">
+        <v>18</v>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>450123</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -24963,19 +24990,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H555" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H555" t="n">
+        <v>18</v>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>077897</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>钻石(硬迎宾)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
@@ -25010,19 +25035,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H556" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H556" t="n">
+        <v>18</v>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>077897</t>
+          <t>450123</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>钻石(硬迎宾)</t>
+          <t>真龙（美人香草）</t>
         </is>
       </c>
     </row>
